--- a/www/download/COUNTRY.ROW.rpA1.xlsx
+++ b/www/download/COUNTRY.ROW.rpA1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Resto do mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.289</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>856.406</t>
+          <t>-0.724574771001668</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>877.09</t>
+          <t>-0.709421265919826</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>896.559</t>
+          <t>-0.709047451676042</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>911.591</t>
+          <t>-0.714964385330047</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>926.097</t>
+          <t>-0.727076022463283</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>955.308</t>
+          <t>-0.72220766808118</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>983.772</t>
+          <t>-0.706101972006724</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>998.606</t>
+          <t>-0.704893930892111</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1035.462</t>
+          <t>-0.67780630168317</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1066.542</t>
+          <t>-0.65512189221256</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1095.297</t>
+          <t>-0.655605105193312</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1124.55</t>
+          <t>-0.647893719479317</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1146.413</t>
+          <t>-0.606981483730396</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1174.341</t>
+          <t>-0.574226139128131</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1192.928</t>
+          <t>-0.570336954898273</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>370.557</t>
+          <t>-0.172392171358465</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>379.509</t>
+          <t>-0.128204309457241</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>390.19</t>
+          <t>-0.135684616468941</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>395.691</t>
+          <t>-0.138817037528654</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>400.131</t>
+          <t>-0.146242749344092</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>413.204</t>
+          <t>-0.154976056001764</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>426.421</t>
+          <t>-0.141272121898506</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>433.848</t>
+          <t>-0.117433721473009</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>450.765</t>
+          <t>-0.0431120472827798</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>467.784</t>
+          <t>0.0136369141746975</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>483.061</t>
+          <t>0.0172460358048483</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>500.543</t>
+          <t>0.0319617212493239</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>514.72</t>
+          <t>0.127326166239921</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>530.955</t>
+          <t>0.167305262709559</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>540.638</t>
+          <t>0.215679721535705</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1581950.09</t>
+          <t>0.967939530294077</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1632216.323</t>
+          <t>1.04075623238768</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1661461.975</t>
+          <t>1.05469062226112</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1675206.949</t>
+          <t>1.11128178794193</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1699153.059</t>
+          <t>1.12523379137722</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1763177.932</t>
+          <t>1.05739532331534</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1837303.246</t>
+          <t>1.12297137683733</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1878897.895</t>
+          <t>1.19517074879198</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1972073.419</t>
+          <t>1.0286407641146</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2057200.705</t>
+          <t>1.39137020417049</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2101215.075</t>
+          <t>1.34210228446034</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2166673.727</t>
+          <t>1.33320545691679</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2217052.892</t>
+          <t>1.39326939383369</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2300250.74</t>
+          <t>1.32748506621706</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2339590.627</t>
+          <t>1.57674091207678</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>684490.338</t>
+          <t>2223676133621.02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>706246.059</t>
+          <t>2279991574253.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>723082.616</t>
+          <t>2348321427454.47</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>727150.964</t>
+          <t>2384924127503.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>734138.16</t>
+          <t>2388326871793.48</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>762635.984</t>
+          <t>2459438902465.44</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>796388.724</t>
+          <t>2544956458265.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>816293.521</t>
+          <t>2648052977146.57</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>858497.817</t>
+          <t>2743654033955.65</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>902286.807</t>
+          <t>2828364162617.91</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>926704.183</t>
+          <t>2906604983556.1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>964398.177</t>
+          <t>3029205917676.6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>995418.423</t>
+          <t>3014420285670.6</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1040011.962</t>
+          <t>3048789405721.77</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1060308.098</t>
+          <t>3134131749670.46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>742448709676.181</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>740936337803.628</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>767960537869.977</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>775860238354.776</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>801483281542.723</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>851036789374.323</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>874236657980.234</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>883623228716.019</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>895601324303.045</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>890900963153.679</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>924148135234.101</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>955103176174.291</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>923173991277.514</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>943236367883.127</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>940203038568.453</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>8352263.02128603</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>8258235.27210211</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>8371833.86634396</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>8816785.78193947</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>8871447.38000383</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>9004536.26217333</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>9520001.90679393</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>9562183.75425118</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>9099271.4080267</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>8438982.49013654</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>7672856.66900778</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>7012930.91975536</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>6114777.60725312</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>5218441.23950145</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>5726246.21156314</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>10502690.5392718</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>10799241.7023113</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>10908166.9034149</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>11001358.342753</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>11643624.5267521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>12358999.2425764</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>12428338.8114015</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>13114018.5663406</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>14722350.3872341</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>16695607.4273276</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>18261211.0876315</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19862016.3567659</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>22684048.1491424</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>25878655.4190609</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>24445260.6923445</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>17310016.1783729</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>17881209.629737</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>18298864.9691078</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>18483400.9900094</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>19277011.1355627</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>20262121.4736135</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>20415399.9136647</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>21715558.8297831</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>24237726.3442001</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>27536961.6993045</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>30307114.1812607</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>33105193.903554</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>37265366.5815706</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>41729815.9122408</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>40015945.5745828</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>-0.078063805228755</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>-0.0468195136731496</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>-0.0584377963229399</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>-0.0627809907874408</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>-0.0840256097083344</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>-0.103874246864209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>-0.0890467505576027</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>-0.0761973034602529</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>-0.0414285977068913</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>0.012780145356978</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>0.00276584253584344</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>0.00973193360849778</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>0.0782565715983214</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>0.10259951538686</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>0.127743747424557</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>834359.584527764</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>875995.799515621</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.12</t>
+          <t>888232.735690991</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>817887.455920437</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>34.61</t>
+          <t>820870.645971099</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>34.03</t>
+          <t>836667.08690153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>817433.866052652</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>808667.728954467</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>900867.030276919</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>1020802.53907012</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>1174139.92751623</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>1288849.39089663</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>1462975.42687985</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>1414733.6337512</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>1300131.74826274</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2003.60450500666</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1952.35397558</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1968.16973915458</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1960.77284404038</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2003.05408599832</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2059.60314543612</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2050.17186770655</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2036.71358453299</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1986.84665958047</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1904.51188035563</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1913.10659346633</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1908.13236655613</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1793.54742041411</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1776.49084590231</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1739.062921192</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>-253257990659.323</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.752</t>
+          <t>-262742109365.069</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.776</t>
+          <t>-223470083346.39</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.711</t>
+          <t>-240626295652.022</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>-256600587572.93</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>-279425361495.227</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>-295816830948.512</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.777</t>
+          <t>-310949217470.719</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-354206416116.78</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.269</t>
+          <t>-382802504415.727</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.609</t>
+          <t>-380729411268.91</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.975</t>
+          <t>-384981493665.879</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3.462</t>
+          <t>-397509524074.089</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-408057068902.044</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>-389606531490.699</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t>-233508594509.679</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>-242042917602.787</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>-199718798330.608</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>-217200020208.576</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>-232249543480.682</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>-250432921530.817</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>-269027922425.72</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.012</t>
+          <t>-279169136794.44</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>-320660220096.736</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>-343829021062.863</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.963</t>
+          <t>-338460604835.578</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>-339778357834.798</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.944</t>
+          <t>-350171803392.202</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>4.811</t>
+          <t>-365902395711.74</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>-353087611305.055</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11.287</t>
+          <t>-19749396149.6439</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.943</t>
+          <t>-20699191762.2815</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11.946</t>
+          <t>-23751285015.7826</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11.365</t>
+          <t>-23426275443.4455</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11.408</t>
+          <t>-24351044092.2485</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11.324</t>
+          <t>-28992439964.4103</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.035</t>
+          <t>-26788908522.792</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.701</t>
+          <t>-31780080676.2785</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11.762</t>
+          <t>-33546196020.0435</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13.123</t>
+          <t>-38973483352.8638</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14.756</t>
+          <t>-42268806433.3313</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>16.116</t>
+          <t>-45203135831.0809</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>18.165</t>
+          <t>-47337720681.8879</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>16.479</t>
+          <t>-42154673190.3038</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>-36518920185.6443</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.003</t>
+          <t>1847.19551317237</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.424</t>
+          <t>1860.9457119255</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>1853.15423680889</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6.264</t>
+          <t>1837.67358218241</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.334</t>
+          <t>1834.74624514354</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6.598</t>
+          <t>1845.66341986478</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.586</t>
+          <t>1867.61072480267</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>1881.52150147071</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7.373</t>
+          <t>1904.53438861543</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>1928.85181902066</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10.019</t>
+          <t>1918.39794505815</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>11.506</t>
+          <t>1926.70218406368</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>13.579</t>
+          <t>1933.90429253473</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>16.651</t>
+          <t>1958.75794578108</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>1961.21733575217</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1847.19551317237</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>1860.9457119255</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>1853.15423680889</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3.221</t>
+          <t>1837.67358218241</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.257</t>
+          <t>1834.74624514354</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.398</t>
+          <t>1845.66341986478</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>1867.61072480267</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.352</t>
+          <t>1881.52150147071</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.736</t>
+          <t>1904.53438861543</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.357</t>
+          <t>1928.85181902067</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>1918.39794505815</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5.791</t>
+          <t>1926.70218406368</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>6.786</t>
+          <t>1933.90429253473</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>8.286</t>
+          <t>1958.75794578108</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>7.707</t>
+          <t>1961.21733575217</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-72.46</t>
+          <t>701304.802261108</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-70.94</t>
+          <t>776487.373711383</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-70.9</t>
+          <t>635985.074643795</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-71.5</t>
+          <t>643545.401190691</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-72.71</t>
+          <t>824736.144773895</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-72.22</t>
+          <t>1081819.67187864</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-70.61</t>
+          <t>1089314.484167</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-70.49</t>
+          <t>1102602.17304957</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-67.78</t>
+          <t>1308815.13215068</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-65.51</t>
+          <t>1623206.21854965</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-65.56</t>
+          <t>2014786.55736804</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-64.79</t>
+          <t>2317531.5351085</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-60.7</t>
+          <t>2656330.43359939</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-57.42</t>
+          <t>3336283.80342492</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-57.03</t>
+          <t>2360037.21884672</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-17.24</t>
+          <t>279111894952.201</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-12.82</t>
+          <t>297716563420.097</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>231483822358.976</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-13.88</t>
+          <t>254301426174.795</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>296945379324.199</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-15.5</t>
+          <t>351504466351.317</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-14.13</t>
+          <t>376147241456.49</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>392494905635.58</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>446618862809.746</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>488313022626.834</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>512521652062.091</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>526305264775.582</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>540744976059.369</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>576153150143.098</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>490016840895.61</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>96.79</t>
+          <t>1058937.18147773</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>1116736.07292101</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>1044258.26035641</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>111.13</t>
+          <t>1011695.46046075</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>1054009.48402831</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>105.74</t>
+          <t>1179943.33914034</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>1176102.18515089</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>119.52</t>
+          <t>1252329.84766961</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>1469427.2441954</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>139.14</t>
+          <t>1797530.83578138</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>134.21</t>
+          <t>2133448.93119307</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>133.32</t>
+          <t>2477531.07134706</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>139.33</t>
+          <t>3027613.30210319</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>132.75</t>
+          <t>3566779.2030106</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>157.67</t>
+          <t>2796920.48323512</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1581950.09</t>
+          <t>81078676847.5082</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1632216.323</t>
+          <t>85408393757.2292</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1661461.975</t>
+          <t>63886221834.7673</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1675206.949</t>
+          <t>66708817226.7861</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1699153.059</t>
+          <t>74117657716.8841</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1763177.932</t>
+          <t>86645906277.9443</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1837303.246</t>
+          <t>93878304849.0181</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1878897.895</t>
+          <t>104658420761.516</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1972073.419</t>
+          <t>115802687614.542</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2057200.705</t>
+          <t>128790714498.676</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2101215.075</t>
+          <t>146480997172.473</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2166673.727</t>
+          <t>159388243227.978</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2217052.892</t>
+          <t>180197341318.829</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2300250.74</t>
+          <t>188405994869.243</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2339590.627</t>
+          <t>142737106375.079</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>684490.338</t>
+          <t>-357632.379216618</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>706246.059</t>
+          <t>-340248.699209626</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>723082.616</t>
+          <t>-408273.185712613</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>727150.964</t>
+          <t>-368150.059270054</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>734138.16</t>
+          <t>-229273.33925441</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>762635.984</t>
+          <t>-98123.6672616966</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>796388.724</t>
+          <t>-86787.7009838913</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>816293.521</t>
+          <t>-149727.674620044</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>858497.817</t>
+          <t>-160612.112044718</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>902286.807</t>
+          <t>-174324.617231727</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>926704.183</t>
+          <t>-118662.373825036</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>964398.177</t>
+          <t>-159999.536238555</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>995418.423</t>
+          <t>-371282.868503794</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1040011.962</t>
+          <t>-230495.399585683</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1060308.098</t>
+          <t>-436883.264388399</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2223676.134</t>
+          <t>198033218104.693</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2279991.574</t>
+          <t>212308169662.868</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2348321.427</t>
+          <t>167597600524.209</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2384924.128</t>
+          <t>187592608948.008</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2388326.872</t>
+          <t>222827721607.315</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2459438.902</t>
+          <t>264858560073.373</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2544956.458</t>
+          <t>282268936607.471</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2648052.977</t>
+          <t>287836484874.063</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2743654.034</t>
+          <t>330816175195.204</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2828364.163</t>
+          <t>359522308128.158</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2906604.984</t>
+          <t>366040654889.618</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3029205.918</t>
+          <t>366917021547.604</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3014420.286</t>
+          <t>360547634740.54</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3048789.406</t>
+          <t>387747155273.855</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3134131.75</t>
+          <t>347279734520.531</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>1693452.24787689</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17.881</t>
+          <t>1815616.36512757</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.299</t>
+          <t>1835440.60484036</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18.483</t>
+          <t>1710026.40859875</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19.277</t>
+          <t>1753515.4220765</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20.262</t>
+          <t>1895478.1988017</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20.415</t>
+          <t>1856320.04175743</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21.716</t>
+          <t>1874128.27508539</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>24.238</t>
+          <t>2096782.94164291</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>27.537</t>
+          <t>2481700.42397383</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>30.307</t>
+          <t>2938719.14606415</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>33.105</t>
+          <t>3403204.25777267</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>37.265</t>
+          <t>3942426.48415527</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>4952165.09986518</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>40.016</t>
+          <t>4395050.71325839</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1349194.712</t>
+          <t>-0.0739203932753493</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1376986.267</t>
+          <t>-0.0733510692176721</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1399861.801</t>
+          <t>-0.0743544942777961</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1419511.753</t>
+          <t>-0.0719684915091149</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1442587.813</t>
+          <t>-0.0719576120389443</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1500149.112</t>
+          <t>-0.0738822163236586</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1549300.1</t>
+          <t>-0.0740785675068383</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1599158.289</t>
+          <t>-0.0755670600218539</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1666535.691</t>
+          <t>-0.0765913131631231</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1714831.804</t>
+          <t>-0.0777855322760167</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1751342.171</t>
+          <t>-0.0795722985676879</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1817422.899</t>
+          <t>-0.0799720171145983</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1834927.741</t>
+          <t>-0.0805374597281697</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1890700.18</t>
+          <t>-0.0858503760875483</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1914603.455</t>
+          <t>-0.0830100473911866</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10.503</t>
+          <t>1656099.77634291</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10.799</t>
+          <t>1752367.9646248</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10.908</t>
+          <t>1775560.24831936</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11.001</t>
+          <t>1710628.53985104</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11.644</t>
+          <t>1729179.1735902</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12.359</t>
+          <t>1808311.6142287</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12.428</t>
+          <t>1805400.01718355</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>13.114</t>
+          <t>1776618.243776</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>14.722</t>
+          <t>1970113.47623266</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>16.696</t>
+          <t>2268914.53320351</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>18.261</t>
+          <t>2608844.29810359</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>19.862</t>
+          <t>2975171.26753475</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>22.684</t>
+          <t>3462290.42564073</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>25.879</t>
+          <t>4230212.3731713</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>24.445</t>
+          <t>3950317.57228416</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>742448.71</t>
+          <t>1912553.25961093</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>740936.338</t>
+          <t>2024580.61430081</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>767960.538</t>
+          <t>2042561.38369465</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>775860.238</t>
+          <t>1955571.25946932</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>801483.282</t>
+          <t>1972638.68944014</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>851036.789</t>
+          <t>2051263.03792785</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>874236.658</t>
+          <t>2042383.82250289</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>883623.229</t>
+          <t>2011676.3093988</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>895601.324</t>
+          <t>2240887.68697854</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>890900.963</t>
+          <t>2581201.91080858</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>924148.135</t>
+          <t>2963357.73251987</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>955103.176</t>
+          <t>3375554.56705043</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>923173.991</t>
+          <t>3944366.02144599</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>943236.368</t>
+          <t>4810828.23995541</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>940203.039</t>
+          <t>4486795.96693829</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>11287271.9902858</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>11942508.9348878</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>11945918.5933329</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>11364521.3171774</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>11407697.1526909</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>11324336.6067459</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>11034687.812736</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>10701325.7988415</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>11762000.0633527</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>13123295.6721036</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>14755636.6807407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>16116254.6275372</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>18165154.8461758</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>16479061.5746225</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>15662341.9588696</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8.352</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.258</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8.372</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>8.817</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8.871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>9.562</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>9.099</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8.439</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7.673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>7.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6.115</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>5.218</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5.726</t>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>684490338211.679</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>706246058804.897</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>723082616373.875</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>727150963878.283</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>734138160140.059</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>762635983824.331</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>796388724368.756</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>816293521413.016</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>858497817332.735</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>902286806961.455</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>926704183455.952</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>964398176874.085</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>995418422823.631</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1040011962123.2</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1060308098055.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1581950090380.27</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1632216323446.71</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1661461975045.46</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1675206949481.46</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1699153059439.56</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1763177932464.47</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1837303245908.48</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1878897894530.26</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1972073419433.81</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2057200705221.21</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2101215074715.22</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2166673727183.3</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2217052892146.03</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2300250740267.96</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2339590626746.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1349194711912.82</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1376986266558.49</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1399861801088.96</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1419511753335.98</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1442587813367.67</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1500149111844.83</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1549300099794.48</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1599158289186</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1666535691327.72</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1714831804475.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1751342171202.12</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1817422899264.31</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1834927740539.67</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1890700180462.9</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1914603455316.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>856406416.7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>877089703.9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>896558927.5</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>911591136.6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>926097036</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>955308488.8</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>983772057.8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>998605592.9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1035462227</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1066541600</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1095296771</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1124550408</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1146412933</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1174341498</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1192927772</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>370556518.425133</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>379509221.724772</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>390190196.806831</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>395691036.171245</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>400130624.103076</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>413204257.946556</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>426421156.075177</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>433847564.736811</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>450765196.188898</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>467784408.353138</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>483061497.143057</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>500543459.622823</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>514719589.10591</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>530954814.689202</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>540637734.903813</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1581950090380.27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1632216323446.71</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1661461975045.46</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1675206949481.46</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1699153059439.56</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1763177932464.47</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1837303245908.48</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1878897894530.26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1972073419433.81</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2057200705221.21</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2101215074715.22</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2166673727183.3</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2217052892146.03</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2300250740267.96</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2339590626746.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>684490338211.679</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>706246058804.897</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>723082616373.875</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>727150963878.283</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>734138160140.059</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>762635983824.331</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>796388724368.756</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>816293521413.016</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>858497817332.735</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>902286806961.455</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>926704183455.952</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>964398176874.085</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>995418422823.631</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1040011962123.2</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1060308098055.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228898648427933</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.231919837016752</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.233019160662987</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.235284951021892</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.240991356161571</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.247797250380012</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.249827856813299</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.256671032957441</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.249986894033455</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.274989880290778</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.282125256882255</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.287263989153529</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289429468407217</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.297021226523762</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.306401074424642</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.453619150842876</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.458991502302581</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.463130386661843</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.465589634981445</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.471018569897122</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.471636483388593</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.473224520750676</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.47349384372661</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.460707877633889</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.472300993256089</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.470266756125835</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.469502423185547</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466965109699573</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.464136590079048</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.463349681517467</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.317482200729191</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.309088660680667</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.30385045267517</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.299125413996663</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.287990073941307</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.280566266231395</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.276947622436025</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.269835123315949</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.289305228332656</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.252709126453133</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.24760798699191</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.243233587660924</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.24360542189321</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.23884218339719</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.230249244057891</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.155282646906169</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.157701180745512</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.159117651873489</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.160829657779038</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.164682133111337</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.168121531150933</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.170713780599449</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.176732786541879</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.182257267892264</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.191332324721546</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.196486156235948</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.200505416481349</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.204207737261477</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.210861564497349</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.219257860870625</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.469773565988899</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.475494398270178</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.479710527481293</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.482224189295601</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.489192905849045</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.491557547666794</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.49292446743076</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.494602048512791</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.496828174229481</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.4980998533911</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.498983843039248</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.499095031787207</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.496367579988465</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.49598976431317</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.496499581531323</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.374943787104932</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.36680442098431</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.361171820645218</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.356946152925361</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.346124961039618</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.340320921182273</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.336361751969791</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.32866516494533</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.320914557878256</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.310567821887355</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.304530000724804</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.300399551731444</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.299424682750058</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.293148671189482</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.284242557598052</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6003296.72858969</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6424492.30466808</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6543783.60858558</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6264479.68287485</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>6333545.30128171</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6598368.92172176</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6585685.88599394</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>6543553.25004621</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7373150.32141448</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>8620444.58875593</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10018945.050815</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>11505716.776729</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>13579035.7644158</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>16651487.3993075</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15730361.8590702</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3100061.91984787</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3310373.4744688</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3370415.8176897</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3221261.55108232</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3257066.93491647</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3398413.01767922</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3375819.90928846</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3352394.52778614</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>3736360.3239901</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4357033.25331906</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5050013.08052761</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5791309.48199016</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6786121.13592133</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>8285953.90396788</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7706866.58207004</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
